--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>20850</v>
+        <v>20800</v>
       </c>
       <c r="C419" t="n">
-        <v>1824113</v>
+        <v>3282321</v>
       </c>
       <c r="D419" t="n">
-        <v>21349</v>
+        <v>21342</v>
       </c>
       <c r="E419" t="n">
-        <v>21100</v>
+        <v>21091</v>
       </c>
       <c r="F419" t="n">
-        <v>21228</v>
+        <v>21189</v>
       </c>
       <c r="G419" t="n">
-        <v>21226</v>
+        <v>21208</v>
       </c>
       <c r="H419" t="n">
-        <v>-0.01366171003717476</v>
+        <v>-0.01449814126394056</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>-0.01449814126394056</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>20600</v>
+      </c>
+      <c r="C420" t="n">
+        <v>2108198</v>
+      </c>
+      <c r="D420" t="n">
+        <v>21340</v>
+      </c>
+      <c r="E420" t="n">
+        <v>21132</v>
+      </c>
+      <c r="F420" t="n">
+        <v>20860</v>
+      </c>
+      <c r="G420" t="n">
+        <v>21111</v>
+      </c>
+      <c r="H420" t="n">
+        <v>-0.01900557620817844</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>20650</v>
+        <v>20600</v>
       </c>
       <c r="C421" t="n">
-        <v>319984</v>
+        <v>1573620</v>
       </c>
       <c r="D421" t="n">
-        <v>21332</v>
+        <v>21325</v>
       </c>
       <c r="E421" t="n">
-        <v>21130</v>
+        <v>21119</v>
       </c>
       <c r="F421" t="n">
-        <v>20904</v>
+        <v>20875</v>
       </c>
       <c r="G421" t="n">
-        <v>21122</v>
+        <v>21106</v>
       </c>
       <c r="H421" t="n">
-        <v>-0.01849442379182153</v>
+        <v>-0.01923791821561338</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>-0.01923791821561338</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>20250</v>
+      </c>
+      <c r="C422" t="n">
+        <v>2244248</v>
+      </c>
+      <c r="D422" t="n">
+        <v>21231</v>
+      </c>
+      <c r="E422" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F422" t="n">
+        <v>20884</v>
+      </c>
+      <c r="G422" t="n">
+        <v>21068</v>
+      </c>
+      <c r="H422" t="n">
+        <v>-0.02100371747211893</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>-0.02100371747211893</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>20100</v>
+      </c>
+      <c r="C423" t="n">
+        <v>2014665</v>
+      </c>
+      <c r="D423" t="n">
+        <v>21151</v>
+      </c>
+      <c r="E423" t="n">
+        <v>21118</v>
+      </c>
+      <c r="F423" t="n">
+        <v>20499</v>
+      </c>
+      <c r="G423" t="n">
+        <v>20923</v>
+      </c>
+      <c r="H423" t="n">
+        <v>-0.02774163568773236</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>-0.02774163568773236</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>19330</v>
+      </c>
+      <c r="C424" t="n">
+        <v>5613200</v>
+      </c>
+      <c r="D424" t="n">
+        <v>21155</v>
+      </c>
+      <c r="E424" t="n">
+        <v>20956</v>
+      </c>
+      <c r="F424" t="n">
+        <v>19942</v>
+      </c>
+      <c r="G424" t="n">
+        <v>20684</v>
+      </c>
+      <c r="H424" t="n">
+        <v>-0.03884758364312269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>-0.03884758364312269</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>19700</v>
+      </c>
+      <c r="C425" t="n">
+        <v>3313049</v>
+      </c>
+      <c r="D425" t="n">
+        <v>21136</v>
+      </c>
+      <c r="E425" t="n">
+        <v>20892</v>
+      </c>
+      <c r="F425" t="n">
+        <v>19793</v>
+      </c>
+      <c r="G425" t="n">
+        <v>20607</v>
+      </c>
+      <c r="H425" t="n">
+        <v>-0.04242565055762082</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>-0.04242565055762082</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>19720</v>
+      </c>
+      <c r="C426" t="n">
+        <v>1897844</v>
+      </c>
+      <c r="D426" t="n">
+        <v>21113</v>
+      </c>
+      <c r="E426" t="n">
+        <v>20855</v>
+      </c>
+      <c r="F426" t="n">
+        <v>19700</v>
+      </c>
+      <c r="G426" t="n">
+        <v>20556</v>
+      </c>
+      <c r="H426" t="n">
+        <v>-0.04479553903345723</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>19960</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1821077</v>
+      </c>
+      <c r="D427" t="n">
+        <v>21095</v>
+      </c>
+      <c r="E427" t="n">
+        <v>20869</v>
+      </c>
+      <c r="F427" t="n">
+        <v>19648</v>
+      </c>
+      <c r="G427" t="n">
+        <v>20538</v>
+      </c>
+      <c r="H427" t="n">
+        <v>-0.04563197026022303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>-0.04563197026022303</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>19700</v>
+      </c>
+      <c r="C428" t="n">
+        <v>2463009</v>
+      </c>
+      <c r="D428" t="n">
+        <v>21003</v>
+      </c>
+      <c r="E428" t="n">
+        <v>20681</v>
+      </c>
+      <c r="F428" t="n">
+        <v>19596</v>
+      </c>
+      <c r="G428" t="n">
+        <v>20427</v>
+      </c>
+      <c r="H428" t="n">
+        <v>-0.05078996282527881</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>-0.05078996282527881</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>19540</v>
+      </c>
+      <c r="C429" t="n">
+        <v>2384269</v>
+      </c>
+      <c r="D429" t="n">
+        <v>20948</v>
+      </c>
+      <c r="E429" t="n">
+        <v>20599</v>
+      </c>
+      <c r="F429" t="n">
+        <v>19711</v>
+      </c>
+      <c r="G429" t="n">
+        <v>20419</v>
+      </c>
+      <c r="H429" t="n">
+        <v>-0.05116171003717473</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>-0.05116171003717473</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>18860</v>
+      </c>
+      <c r="C430" t="n">
+        <v>3531134</v>
+      </c>
+      <c r="D430" t="n">
+        <v>20882</v>
+      </c>
+      <c r="E430" t="n">
+        <v>20454</v>
+      </c>
+      <c r="F430" t="n">
+        <v>19466</v>
+      </c>
+      <c r="G430" t="n">
+        <v>20267</v>
+      </c>
+      <c r="H430" t="n">
+        <v>-0.05822490706319705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>-0.05822490706319705</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>18010</v>
+      </c>
+      <c r="C431" t="n">
+        <v>3670531</v>
+      </c>
+      <c r="D431" t="n">
+        <v>20694</v>
+      </c>
+      <c r="E431" t="n">
+        <v>20122</v>
+      </c>
+      <c r="F431" t="n">
+        <v>19046</v>
+      </c>
+      <c r="G431" t="n">
+        <v>19954</v>
+      </c>
+      <c r="H431" t="n">
+        <v>-0.07276951672862453</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>-0.07276951672862453</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>18360</v>
+      </c>
+      <c r="C432" t="n">
+        <v>4835567</v>
+      </c>
+      <c r="D432" t="n">
+        <v>20533</v>
+      </c>
+      <c r="E432" t="n">
+        <v>19969</v>
+      </c>
+      <c r="F432" t="n">
+        <v>18751</v>
+      </c>
+      <c r="G432" t="n">
+        <v>19751</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-0.08220260223048326</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>-0.08220260223048326</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>18950</v>
+      </c>
+      <c r="C433" t="n">
+        <v>5280075</v>
+      </c>
+      <c r="D433" t="n">
+        <v>20408</v>
+      </c>
+      <c r="E433" t="n">
+        <v>19708</v>
+      </c>
+      <c r="F433" t="n">
+        <v>18685</v>
+      </c>
+      <c r="G433" t="n">
+        <v>19601</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-0.08917286245353162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>-0.08917286245353162</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>18170</v>
+      </c>
+      <c r="C434" t="n">
+        <v>3690393</v>
+      </c>
+      <c r="D434" t="n">
+        <v>20336</v>
+      </c>
+      <c r="E434" t="n">
+        <v>19539</v>
+      </c>
+      <c r="F434" t="n">
+        <v>18498</v>
+      </c>
+      <c r="G434" t="n">
+        <v>19457</v>
+      </c>
+      <c r="H434" t="n">
+        <v>-0.09586431226765801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>-0.09586431226765801</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>18400</v>
+      </c>
+      <c r="C435" t="n">
+        <v>3392293</v>
+      </c>
+      <c r="D435" t="n">
+        <v>20280</v>
+      </c>
+      <c r="E435" t="n">
+        <v>19446</v>
+      </c>
+      <c r="F435" t="n">
+        <v>18421</v>
+      </c>
+      <c r="G435" t="n">
+        <v>19382</v>
+      </c>
+      <c r="H435" t="n">
+        <v>-0.0993494423791822</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>-0.0993494423791822</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>18300</v>
+      </c>
+      <c r="C436" t="n">
+        <v>2884033</v>
+      </c>
+      <c r="D436" t="n">
+        <v>20194</v>
+      </c>
+      <c r="E436" t="n">
+        <v>19125</v>
+      </c>
+      <c r="F436" t="n">
+        <v>18478</v>
+      </c>
+      <c r="G436" t="n">
+        <v>19266</v>
+      </c>
+      <c r="H436" t="n">
+        <v>-0.1047397769516729</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>-0.1047397769516729</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>17320</v>
+      </c>
+      <c r="C437" t="n">
+        <v>3296664</v>
+      </c>
+      <c r="D437" t="n">
+        <v>20103</v>
+      </c>
+      <c r="E437" t="n">
+        <v>19019</v>
+      </c>
+      <c r="F437" t="n">
+        <v>18303</v>
+      </c>
+      <c r="G437" t="n">
+        <v>19142</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-0.1105018587360594</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>-0.1105018587360594</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>17680</v>
+      </c>
+      <c r="C438" t="n">
+        <v>2740275</v>
+      </c>
+      <c r="D438" t="n">
+        <v>20044</v>
+      </c>
+      <c r="E438" t="n">
+        <v>18895</v>
+      </c>
+      <c r="F438" t="n">
+        <v>17983</v>
+      </c>
+      <c r="G438" t="n">
+        <v>18974</v>
+      </c>
+      <c r="H438" t="n">
+        <v>-0.1183085501858736</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>-0.1183085501858736</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>17320</v>
+      </c>
+      <c r="C439" t="n">
+        <v>1832819</v>
+      </c>
+      <c r="D439" t="n">
+        <v>20002</v>
+      </c>
+      <c r="E439" t="n">
+        <v>18798</v>
+      </c>
+      <c r="F439" t="n">
+        <v>17849</v>
+      </c>
+      <c r="G439" t="n">
+        <v>18883</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.1225371747211896</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>-0.1225371747211896</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>16830</v>
+      </c>
+      <c r="C440" t="n">
+        <v>2771984</v>
+      </c>
+      <c r="D440" t="n">
+        <v>19929</v>
+      </c>
+      <c r="E440" t="n">
+        <v>18646</v>
+      </c>
+      <c r="F440" t="n">
+        <v>17501</v>
+      </c>
+      <c r="G440" t="n">
+        <v>18692</v>
+      </c>
+      <c r="H440" t="n">
+        <v>-0.1314126394052044</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>-0.1314126394052044</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>16300</v>
+      </c>
+      <c r="C441" t="n">
+        <v>2267049</v>
+      </c>
+      <c r="D441" t="n">
+        <v>19838</v>
+      </c>
+      <c r="E441" t="n">
+        <v>18557</v>
+      </c>
+      <c r="F441" t="n">
+        <v>17112</v>
+      </c>
+      <c r="G441" t="n">
+        <v>18502</v>
+      </c>
+      <c r="H441" t="n">
+        <v>-0.1402416356877323</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>-0.1402416356877323</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>16390</v>
+      </c>
+      <c r="C442" t="n">
+        <v>3260968</v>
+      </c>
+      <c r="D442" t="n">
+        <v>19728</v>
+      </c>
+      <c r="E442" t="n">
+        <v>18445</v>
+      </c>
+      <c r="F442" t="n">
+        <v>16876</v>
+      </c>
+      <c r="G442" t="n">
+        <v>18349</v>
+      </c>
+      <c r="H442" t="n">
+        <v>-0.1473513011152416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>-0.1473513011152416</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>16510</v>
+      </c>
+      <c r="C443" t="n">
+        <v>4080989</v>
+      </c>
+      <c r="D443" t="n">
+        <v>19595</v>
+      </c>
+      <c r="E443" t="n">
+        <v>18272</v>
+      </c>
+      <c r="F443" t="n">
+        <v>16616</v>
+      </c>
+      <c r="G443" t="n">
+        <v>18161</v>
+      </c>
+      <c r="H443" t="n">
+        <v>-0.1560873605947956</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>-0.1560873605947956</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>15720</v>
+      </c>
+      <c r="C444" t="n">
+        <v>5306050</v>
+      </c>
+      <c r="D444" t="n">
+        <v>19433</v>
+      </c>
+      <c r="E444" t="n">
+        <v>17971</v>
+      </c>
+      <c r="F444" t="n">
+        <v>16274</v>
+      </c>
+      <c r="G444" t="n">
+        <v>17893</v>
+      </c>
+      <c r="H444" t="n">
+        <v>-0.1685408921933086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성중공업_일별_기준주가.xlsx
+++ b/data/삼성중공업_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>-0.1685408921933086</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>15880</v>
+      </c>
+      <c r="C445" t="n">
+        <v>5014673</v>
+      </c>
+      <c r="D445" t="n">
+        <v>19298</v>
+      </c>
+      <c r="E445" t="n">
+        <v>17727</v>
+      </c>
+      <c r="F445" t="n">
+        <v>16098</v>
+      </c>
+      <c r="G445" t="n">
+        <v>17707</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-0.1771840148698884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
